--- a/toolkit/sac_team_data.xlsx
+++ b/toolkit/sac_team_data.xlsx
@@ -1,173 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://apcdeloitte-my.sharepoint.com/personal/pinpibul_deloitte_com/Documents/Desktop/Coding SAC/SAC_ROLE/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{958DCC5C-F877-4B7E-BE82-615F79D1D315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2C6005E-493F-49C0-9DC2-2469229CB375}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Create_Teams" sheetId="1" r:id="rId1"/>
-    <sheet name="Assign_Roles" sheetId="2" r:id="rId2"/>
-    <sheet name="Users" sheetId="3" r:id="rId3"/>
+    <sheet name="Create_Teams" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Assign_Roles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Users" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
-  <si>
-    <t>UserName</t>
-  </si>
-  <si>
-    <t>TeamID</t>
-  </si>
-  <si>
-    <t>RoleID</t>
-  </si>
-  <si>
-    <t>Team ID</t>
-  </si>
-  <si>
-    <t>Team Description</t>
-  </si>
-  <si>
-    <t>Finance planning team for Company Alpha</t>
-  </si>
-  <si>
-    <t>Finance read-only access for Company Alpha</t>
-  </si>
-  <si>
-    <t>Finance planning team for Company Beta</t>
-  </si>
-  <si>
-    <t>Finance read-only access for Company Beta</t>
-  </si>
-  <si>
-    <t>Operations planning team for Company Alpha</t>
-  </si>
-  <si>
-    <t>Operations planning team for Company Beta</t>
-  </si>
-  <si>
-    <t>Capital expenditure planning team for Company Alpha</t>
-  </si>
-  <si>
-    <t>Capital expenditure planning team for Company Beta</t>
-  </si>
-  <si>
-    <t>Finance model admin access across all entities</t>
-  </si>
-  <si>
-    <t>System-wide administration team</t>
-  </si>
-  <si>
-    <t>Alice</t>
-  </si>
-  <si>
-    <t>R_Planner</t>
-  </si>
-  <si>
-    <t>R_Viewer</t>
-  </si>
-  <si>
-    <t>T_Alpha_Finance_Planners</t>
-  </si>
-  <si>
-    <t>T_Alpha_Finance_Viewers</t>
-  </si>
-  <si>
-    <t>T_Beta_Finance_Planners</t>
-  </si>
-  <si>
-    <t>T_Beta_Finance_Viewers</t>
-  </si>
-  <si>
-    <t>T_Alpha_Operations_Planners</t>
-  </si>
-  <si>
-    <t>T_Beta_Operations_Planners</t>
-  </si>
-  <si>
-    <t>T_Alpha_Capital_Planners</t>
-  </si>
-  <si>
-    <t>T_Beta_Capital_Planners</t>
-  </si>
-  <si>
-    <t>T_All_Finance_Admins</t>
-  </si>
-  <si>
-    <t>T_SAC_System_Admins</t>
-  </si>
-  <si>
-    <t>R_Finance_Admin</t>
-  </si>
-  <si>
-    <t>R_System_Admin</t>
-  </si>
-  <si>
-    <t>Miya</t>
-  </si>
-  <si>
-    <t>Brandon</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -211,48 +92,35 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{22FDC577-9EA6-46A6-BA4C-A35E2D8DAAAD}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFC9DBED"/>
-    </mruColors>
-  </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -540,104 +408,149 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="34.26953125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="49.6328125" style="5" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="4"/>
+    <col width="34.26953125" customWidth="1" style="4" min="1" max="1"/>
+    <col width="49.6328125" customWidth="1" style="5" min="2" max="2"/>
+    <col width="8.7265625" customWidth="1" style="4" min="3" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>14</v>
+    <row r="1" ht="16.5" customHeight="1" s="4">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Team ID</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Team Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" s="4">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>T_Alpha_Finance_Planners</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Finance planning team for Company Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16.5" customHeight="1" s="4">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>T_Alpha_Finance_Viewers</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Finance read-only access for Company Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>T_Beta_Finance_Planners</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Finance planning team for Company Beta</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="4">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>T_Beta_Finance_Viewers</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Finance read-only access for Company Beta</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="4">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>T_Alpha_Operations_Planners</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Operations planning team for Company Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="4">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>T_Beta_Operations_Planners</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Operations planning team for Company Beta</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="4">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>T_Alpha_Capital_Planners</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Capital expenditure planning team for Company Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="4">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>T_Beta_Capital_Planners</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Capital expenditure planning team for Company Beta</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="4">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>T_All_Finance_Admins</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Finance model admin access across all entities</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="4">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>T_SAC_System_Admins</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>System-wide administration team</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -646,103 +559,148 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="29.453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col width="29.453125" customWidth="1" style="5" min="1" max="1"/>
+    <col width="32.81640625" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>29</v>
+    <row r="1" ht="18.75" customHeight="1" s="4">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>TeamID</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>RoleID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1" s="4">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>T_Alpha_Finance_Planners</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>PROFILE:sap.epm:Planner_Reporter</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1" s="4">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>T_Alpha_Finance_Viewers</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>PROFILE:sap.epm:Viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18.75" customHeight="1" s="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>T_Beta_Finance_Planners</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>PROFILE:sap.epm:Planner_Reporter</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1" s="4">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>T_Beta_Finance_Viewers</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>PROFILE:sap.epm:Viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1" s="4">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>T_Alpha_Operations_Planners</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>PROFILE:sap.epm:Planner_Reporter</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1" s="4">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>T_Beta_Operations_Planners</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>PROFILE:sap.epm:Planner_Reporter</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18.75" customHeight="1" s="4">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>T_Alpha_Capital_Planners</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>PROFILE:sap.epm:Planner_Reporter</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18.75" customHeight="1" s="4">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>T_Beta_Capital_Planners</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>PROFILE:sap.epm:Planner_Reporter</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>T_All_Finance_Admins</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>PROFILE:sap.epm:Admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>T_SAC_System_Admins</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>PROFILE:sap.epm:Admin</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -751,56 +709,67 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.453125" style="1" bestFit="1" customWidth="1"/>
+    <col width="14.54296875" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="29.453125" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>27</v>
+    <row r="1" ht="19.5" customHeight="1" s="4">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>UserName</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>TeamID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="19.5" customHeight="1" s="4">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Miya</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>T_Alpha_Finance_Planners</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>T_Alpha_Operations_Planners</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Brandon</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>T_SAC_System_Admins</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{ea60d57e-af5b-4752-ac57-3e4f28ca11dc}" enabled="1" method="Standard" siteId="{36da45f1-dd2c-4d1f-af13-5abe46b99921}" removed="0"/>
-</clbl:labelList>
 </file>